--- a/201025_Results_Cali/output/m2/21102025_mod2_by_main_activity.xlsx
+++ b/201025_Results_Cali/output/m2/21102025_mod2_by_main_activity.xlsx
@@ -3831,32 +3831,32 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Estudio</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>13 (24.1%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>13 (76.5%)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>24 (8.0%)</t>
+          <t>9 (3.0%)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>3 (23.1%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>15 (31.2%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="I78">
@@ -3876,12 +3876,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cuidado y familia (centro educativo, niños/as o jóvenes)</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>1 (1.9%)</t>
+          <t>2 (3.7%)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1 (0.3%)</t>
+          <t>3 (1.0%)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1 (7.7%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3921,22 +3921,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cuidado y familia (otro lugar, niños/as o jóvenes)</t>
+          <t>Recreación y actividades personales</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1 (1.9%)</t>
+          <t>6 (11.1%)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (5.9%)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>7 (2.3%)</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (6.2%)</t>
         </is>
       </c>
       <c r="I80">
@@ -3966,32 +3966,32 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Estudio</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>21 (38.9%)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>13 (76.5%)</t>
+          <t>1 (5.9%)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>9 (3.0%)</t>
+          <t>28 (9.3%)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>5 (38.5%)</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>22 (45.8%)</t>
         </is>
       </c>
       <c r="I81">
@@ -4011,32 +4011,32 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Trabajo</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2 (3.7%)</t>
+          <t>8 (14.8%)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (11.8%)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>3 (1.0%)</t>
+          <t>224 (74.4%)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>4 (30.8%)</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>5 (10.4%)</t>
         </is>
       </c>
       <c r="I82">
@@ -4056,32 +4056,32 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Trámites</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>27 (50.0%)</t>
+          <t>5 (9.3%)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2 (11.8%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>35 (11.6%)</t>
+          <t>6 (2.0%)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>5 (38.5%)</t>
+          <t>1 (7.7%)</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>25 (52.1%)</t>
+          <t>5 (10.4%)</t>
         </is>
       </c>
       <c r="I83">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Trabajo</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>8 (14.8%)</t>
+          <t>10 (18.5%)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2 (11.8%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>224 (74.4%)</t>
+          <t>19 (6.3%)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>4 (30.8%)</t>
+          <t>3 (23.1%)</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>5 (10.4%)</t>
+          <t>10 (20.8%)</t>
         </is>
       </c>
       <c r="I84">
